--- a/docs/test-cases/Aros_Regression_Storefront_Master.xlsx
+++ b/docs/test-cases/Aros_Regression_Storefront_Master.xlsx
@@ -863,6 +863,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -895,7 +896,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Логин: +998998987882   Пароль: Sh2004Sh</t>
+          <t>Логин: +998998987882   Пароль: &lt;пароль в .env&gt; в .env&gt;</t>
         </is>
       </c>
     </row>
@@ -2440,6 +2441,7 @@
         <v/>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
@@ -2766,7 +2768,7 @@
       <c r="I2" s="27" t="inlineStr">
         <is>
           <t>Телефон: +998998987882
-Пароль: Sh2004Sh</t>
+Пароль: &lt;пароль в .env&gt; в .env&gt;</t>
         </is>
       </c>
       <c r="J2" s="27" t="inlineStr">
@@ -18537,6 +18539,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
